--- a/Project 4 - Group L - Gantt Chart.xlsx
+++ b/Project 4 - Group L - Gantt Chart.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="31" documentId="8_{2737DE72-F959-4A9C-94DD-57F6D49EDD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E8BC45-5CAA-4187-A315-FD861A08406A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -1074,28 +1074,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1113,17 +1110,20 @@
     <xf numFmtId="166" fontId="11" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -3941,92 +3941,92 @@
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="97" t="s">
+      <c r="I1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
       <c r="P1" s="11"/>
-      <c r="Q1" s="96">
+      <c r="Q1" s="95">
         <v>46113</v>
       </c>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AL1" s="86" t="s">
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AL1" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="AM1" s="87"/>
-      <c r="AN1" s="87"/>
-      <c r="AO1" s="87"/>
-      <c r="AP1" s="87"/>
-      <c r="AQ1" s="87"/>
-      <c r="AR1" s="87"/>
-      <c r="AS1" s="88"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="101"/>
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="102"/>
     </row>
     <row r="2" spans="1:45" ht="24.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="I2" s="97" t="s">
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="I2" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
       <c r="P2" s="11"/>
-      <c r="Q2" s="94">
+      <c r="Q2" s="93">
         <v>1</v>
       </c>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="94"/>
       <c r="AL2" s="72"/>
-      <c r="AN2" s="89" t="s">
+      <c r="AN2" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="AO2" s="89"/>
-      <c r="AP2" s="89"/>
-      <c r="AQ2" s="89"/>
+      <c r="AO2" s="103"/>
+      <c r="AP2" s="103"/>
+      <c r="AQ2" s="103"/>
       <c r="AR2" s="72"/>
       <c r="AS2" s="80"/>
     </row>
     <row r="3" spans="1:45" s="12" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
       <c r="AL3" s="73"/>
       <c r="AM3" s="75"/>
-      <c r="AN3" s="89"/>
-      <c r="AO3" s="89"/>
-      <c r="AP3" s="89"/>
-      <c r="AQ3" s="89"/>
+      <c r="AN3" s="103"/>
+      <c r="AO3" s="103"/>
+      <c r="AP3" s="103"/>
+      <c r="AQ3" s="103"/>
       <c r="AR3" s="73"/>
       <c r="AS3" s="81"/>
     </row>
@@ -4034,46 +4034,46 @@
       <c r="A4" s="5"/>
       <c r="B4" s="13"/>
       <c r="E4" s="14"/>
-      <c r="I4" s="100">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>46111</v>
       </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91">
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92">
         <f>P5</f>
         <v>46118</v>
       </c>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="91"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="91">
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="92"/>
+      <c r="V4" s="92"/>
+      <c r="W4" s="92">
         <f>W5</f>
         <v>46125</v>
       </c>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="91"/>
-      <c r="Z4" s="91"/>
-      <c r="AA4" s="91"/>
-      <c r="AB4" s="91"/>
-      <c r="AC4" s="91"/>
-      <c r="AD4" s="91">
+      <c r="X4" s="92"/>
+      <c r="Y4" s="92"/>
+      <c r="Z4" s="92"/>
+      <c r="AA4" s="92"/>
+      <c r="AB4" s="92"/>
+      <c r="AC4" s="92"/>
+      <c r="AD4" s="92">
         <f t="shared" ref="AD4" si="0">AD5</f>
         <v>46132</v>
       </c>
-      <c r="AE4" s="91"/>
-      <c r="AF4" s="91"/>
-      <c r="AG4" s="91"/>
-      <c r="AH4" s="91"/>
-      <c r="AI4" s="91"/>
-      <c r="AJ4" s="91"/>
+      <c r="AE4" s="92"/>
+      <c r="AF4" s="92"/>
+      <c r="AG4" s="92"/>
+      <c r="AH4" s="92"/>
+      <c r="AI4" s="92"/>
+      <c r="AJ4" s="92"/>
       <c r="AL4" s="82"/>
       <c r="AM4" s="83"/>
       <c r="AN4" s="83"/>
@@ -4084,20 +4084,20 @@
       <c r="AS4" s="84"/>
     </row>
     <row r="5" spans="1:45" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="101"/>
-      <c r="B5" s="102" t="s">
+      <c r="A5" s="86"/>
+      <c r="B5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="104" t="s">
+      <c r="C5" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="92" t="s">
+      <c r="F5" s="91" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="15">
@@ -4216,12 +4216,12 @@
       <c r="AS5" s="85"/>
     </row>
     <row r="6" spans="1:45" s="12" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="101"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
       <c r="I6" s="18" t="str">
         <f t="shared" ref="I6:AJ6" si="2">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -4426,22 +4426,22 @@
       <c r="AH8" s="28"/>
       <c r="AI8" s="28"/>
       <c r="AJ8" s="28"/>
-      <c r="AL8" s="90" t="s">
+      <c r="AL8" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="90" t="s">
+      <c r="AM8" s="104"/>
+      <c r="AN8" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="AO8" s="90"/>
-      <c r="AP8" s="90" t="s">
+      <c r="AO8" s="104"/>
+      <c r="AP8" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="AQ8" s="90"/>
-      <c r="AR8" s="90" t="s">
+      <c r="AQ8" s="104"/>
+      <c r="AR8" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="AS8" s="90"/>
+      <c r="AS8" s="104"/>
     </row>
     <row r="9" spans="1:45" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
@@ -7206,11 +7206,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="AL1:AS1"/>
+    <mergeCell ref="AN2:AQ3"/>
+    <mergeCell ref="AL8:AM8"/>
+    <mergeCell ref="AN8:AO8"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="AR8:AS8"/>
     <mergeCell ref="AD4:AJ4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="Q2:Z2"/>
@@ -7221,12 +7222,11 @@
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
-    <mergeCell ref="AL1:AS1"/>
-    <mergeCell ref="AN2:AQ3"/>
-    <mergeCell ref="AL8:AM8"/>
-    <mergeCell ref="AN8:AO8"/>
-    <mergeCell ref="AP8:AQ8"/>
-    <mergeCell ref="AR8:AS8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D58">
     <cfRule type="dataBar" priority="87">
@@ -7492,23 +7492,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d94ee4e4-02cb-4da0-9dbe-ce518434d583" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100496DD1FC206C7E4C8297AEA9970FAC90" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bdc3eefcce20f052996132159226e429">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d94ee4e4-02cb-4da0-9dbe-ce518434d583" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c4b9b742bc415e6b5f4f276646a238f" ns3:_="">
     <xsd:import namespace="d94ee4e4-02cb-4da0-9dbe-ce518434d583"/>
@@ -7696,25 +7679,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d94ee4e4-02cb-4da0-9dbe-ce518434d583" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d94ee4e4-02cb-4da0-9dbe-ce518434d583"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26D5C4D-B1F7-431E-9F6D-FE05EC6432DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7732,6 +7714,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d94ee4e4-02cb-4da0-9dbe-ce518434d583"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>